--- a/data/mock/mock-restaurants-cafes.xlsx
+++ b/data/mock/mock-restaurants-cafes.xlsx
@@ -4408,7 +4408,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>현재 실제 후보 catalogue.json과 자동으로 섞거나 추천 서비스에 연결하지 않았습니다.</t>
+          <t>웹서비스의 [가상] 업소 검색과 코스 테스트에 연결했습니다. 실제 관광 후보와는 별도 관리하며 실제 지도·예약 링크는 없습니다.</t>
         </is>
       </c>
     </row>
